--- a/Assets/GameResource/Excel/商店配置.xlsx
+++ b/Assets/GameResource/Excel/商店配置.xlsx
@@ -8,24 +8,43 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\LastGame\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA1A846-223D-4C71-ADD9-BBA00E133A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73DCE10-3A5F-449F-9ECB-2EDE006B7C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopCardPackInfo" sheetId="1" r:id="rId1"/>
     <sheet name="RemoveCardCostInfo" sheetId="2" r:id="rId2"/>
+    <sheet name="PotionInfo" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="58">
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Increment</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>唯一ID</t>
+  </si>
+  <si>
+    <t>删牌起步价</t>
+  </si>
+  <si>
+    <t>每次删牌加价</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -47,13 +66,7 @@
     <t>Address</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>唯一ID</t>
   </si>
   <si>
     <t xml:space="preserve">卡包名称
@@ -80,6 +93,9 @@
     <t>封面素材资源路径</t>
   </si>
   <si>
+    <t>普通卡包</t>
+  </si>
+  <si>
     <t>从3张随机卡牌中\n选择1张</t>
   </si>
   <si>
@@ -89,55 +105,103 @@
     <t>bull</t>
   </si>
   <si>
+    <t>大普通卡包</t>
+  </si>
+  <si>
     <t>从6张随机卡牌中\n选择2张</t>
   </si>
   <si>
+    <t>罕见卡包</t>
+  </si>
+  <si>
+    <t>从3张罕见及以上卡牌中\n选择1张</t>
+  </si>
+  <si>
     <t>罕见,史诗</t>
   </si>
   <si>
+    <t>大罕见卡包</t>
+  </si>
+  <si>
+    <t>从5张罕见及以上卡牌中\n选择2张</t>
+  </si>
+  <si>
+    <t>史诗卡包</t>
+  </si>
+  <si>
     <t>从3张史诗卡牌中\n选择1张</t>
   </si>
   <si>
     <t>史诗</t>
   </si>
   <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>Increment</t>
-  </si>
-  <si>
-    <t>删牌起步价</t>
-  </si>
-  <si>
-    <t>每次删牌加价</t>
-  </si>
-  <si>
-    <t>从3张罕见及以上卡牌中\n选择1张</t>
+    <t>EffectType</t>
+  </si>
+  <si>
+    <t>EffectValue</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>效果类型</t>
+  </si>
+  <si>
+    <t>效果数值</t>
+  </si>
+  <si>
+    <t>红药水</t>
+  </si>
+  <si>
+    <t>回复15点生命值</t>
+  </si>
+  <si>
+    <t>Heal</t>
+  </si>
+  <si>
+    <t>能量药水</t>
+  </si>
+  <si>
+    <t>回复2点能量</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>铁皮药水</t>
+  </si>
+  <si>
+    <t>获得12点护甲</t>
+  </si>
+  <si>
+    <t>Block</t>
+  </si>
+  <si>
+    <t>陨石药水</t>
+  </si>
+  <si>
+    <t>对目标造成10点伤害</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>Address</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>从5张罕见及以上卡牌中\n选择2张</t>
+    <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>普通卡包</t>
+    <t>美术资源地址</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>大普通卡包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>罕见卡包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大罕见卡包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>史诗卡包</t>
+    <t>能量药水</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -504,77 +568,77 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -582,10 +646,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <v>60</v>
@@ -597,10 +661,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -608,10 +672,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D5">
         <v>140</v>
@@ -623,10 +687,10 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -634,7 +698,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>29</v>
@@ -649,10 +713,10 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -660,10 +724,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7">
         <v>300</v>
@@ -675,10 +739,10 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -686,10 +750,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D8">
         <v>450</v>
@@ -701,10 +765,10 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -727,32 +791,32 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,6 +828,184 @@
       </c>
       <c r="C4">
         <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="19.109375" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5">
+        <v>60</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7">
+        <v>70</v>
+      </c>
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
